--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2816-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2816-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84F919FC-B1FA-4AAB-B7F7-1D28F6A9F4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFD5B38B-B675-4C7E-8B61-851D61CE0753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{5BE0234E-12D4-406F-98EF-42ADAA4DD987}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{61192107-03FE-4C51-BEED-C0A0768C6F2C}"/>
   </bookViews>
   <sheets>
     <sheet name="2816-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1523,27 +1523,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4746BF9-C90B-41A4-81D8-BA99E1B189D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ED5BC01-7235-4F53-8557-A38ED47B8A78}">
   <dimension ref="A1:X40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1577,7 +1576,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1613,7 +1612,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1665,7 +1664,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1733,7 +1732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1805,7 +1804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1877,7 +1876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1949,7 +1948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2021,7 +2020,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2093,7 +2092,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2019</v>
       </c>
@@ -2165,7 +2164,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="43"/>
       <c r="B11" s="44"/>
       <c r="C11" s="18" t="s">
@@ -2193,7 +2192,7 @@
       <c r="W11" s="50"/>
       <c r="X11" s="46"/>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2018</v>
       </c>
@@ -2265,7 +2264,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2017</v>
       </c>
@@ -2337,7 +2336,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2016</v>
       </c>
@@ -2409,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2015</v>
       </c>
@@ -2481,7 +2480,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2014</v>
       </c>
@@ -2553,7 +2552,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2013</v>
       </c>
@@ -2625,7 +2624,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2012</v>
       </c>
@@ -2697,7 +2696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2011</v>
       </c>
@@ -2769,7 +2768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2010</v>
       </c>
@@ -2841,7 +2840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2009</v>
       </c>
@@ -2913,7 +2912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2008</v>
       </c>
@@ -2985,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2007</v>
       </c>
@@ -3057,7 +3056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2006</v>
       </c>
@@ -3129,7 +3128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2005</v>
       </c>
@@ -3201,7 +3200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2004</v>
       </c>
@@ -3273,7 +3272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2003</v>
       </c>
@@ -3345,7 +3344,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2002</v>
       </c>
@@ -3417,7 +3416,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2001</v>
       </c>
@@ -3489,7 +3488,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2000</v>
       </c>
@@ -3561,7 +3560,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>1999</v>
       </c>
@@ -3633,7 +3632,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1998</v>
       </c>
@@ -3705,7 +3704,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>1997</v>
       </c>
@@ -3777,7 +3776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1996</v>
       </c>
@@ -3849,7 +3848,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>1995</v>
       </c>
@@ -3921,7 +3920,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>1994</v>
       </c>
@@ -3993,7 +3992,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>1993</v>
       </c>
@@ -4065,7 +4064,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>1992</v>
       </c>
@@ -4137,7 +4136,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>1991</v>
       </c>
@@ -4209,7 +4208,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37" t="s">
         <v>53</v>
       </c>
